--- a/output/pdf_financials_xlsx/APS.xlsx
+++ b/output/pdf_financials_xlsx/APS.xlsx
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="R10" s="3" t="n">
-        <v>33.273</v>
+        <v>52.356</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>26.257</v>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>1.151</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="13">
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-51.207</v>
+        <v>-52.358</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-25.43</v>
+        <v>-25.787</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>-25.468</v>
+        <v>-25.573</v>
       </c>
     </row>
     <row r="28">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-51.207</v>
+        <v>-52.358</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-25.43</v>
+        <v>-25.787</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-25.468</v>
+        <v>-25.573</v>
       </c>
     </row>
     <row r="30">
@@ -9061,10 +9061,10 @@
         <v>0</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.405</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="T124" s="3" t="n">
         <v>0</v>
@@ -9135,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.405</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="T125" s="3" t="n">
         <v>0</v>
@@ -30881,7 +30881,11 @@
           <t>Operating lease payments</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -52185,7 +52189,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -55291,7 +55295,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -55404,7 +55408,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">

--- a/output/pdf_financials_xlsx/APS.xlsx
+++ b/output/pdf_financials_xlsx/APS.xlsx
@@ -1294,10 +1294,10 @@
         <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.057</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.981</v>
+        <v>-4.924</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.608</v>
+        <v>-4.594</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="29">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.981</v>
+        <v>-4.924</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.608</v>
+        <v>-4.594</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-52.358</v>
+        <v>-52.27</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-25.787</v>
+        <v>-25.755</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-25.573</v>
+        <v>-25.551</v>
       </c>
     </row>
     <row r="30">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-3802.290076335878</v>
+        <v>-3758.778625954199</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -7285,13 +7285,13 @@
         <v>0.15</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="T100" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="101">
@@ -8176,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="T112" s="3" t="n">
         <v>0</v>
@@ -26477,7 +26477,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -26586,7 +26590,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -27793,7 +27801,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -30332,7 +30344,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -30441,7 +30457,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -65600,7 +65620,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
